--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484788_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484788_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>J. NAVARRO MORALES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6551</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0349</v>
+        <v>0.5447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6202</v>
+        <v>0.3096</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1557</v>
+        <v>-1.1914</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.1602</v>
+        <v>-0.2272</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2588</v>
+        <v>-0.026</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1439</v>
+        <v>-0.2317</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4028</v>
+        <v>0.2057</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8968</v>
+        <v>-1.1654</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1394</v>
+        <v>-0.7325</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7574</v>
+        <v>-0.4329</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0192</v>
+        <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3767</v>
+        <v>-0.1432</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5771</v>
+        <v>0.2689</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2004</v>
+        <v>-0.4121</v>
       </c>
       <c r="V2" t="n">
         <v>0.3018</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6036</v>
+        <v>0.3018</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1033</v>
+        <v>0.4893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.803</v>
+        <v>1.0567</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6997</v>
+        <v>-0.5674</v>
       </c>
       <c r="G3" t="n">
         <v>0.6674</v>
@@ -688,13 +688,13 @@
         <v>0.5661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2058</v>
+        <v>0.1802</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2228</v>
+        <v>0.0308</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0171</v>
+        <v>0.1493</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9244</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NAVARRO MORALES</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.3482</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0399</v>
+        <v>-0.7833</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1244</v>
+        <v>0.435</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1914</v>
+        <v>-2.1557</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2272</v>
+        <v>-1.1602</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.026</v>
+        <v>-0.2588</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2317</v>
+        <v>0.1439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2057</v>
+        <v>-0.4028</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1654</v>
+        <v>-1.8968</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7325</v>
+        <v>-1.1394</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4329</v>
+        <v>-0.7574</v>
       </c>
       <c r="P4" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887</v>
+        <v>3.0192</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9129</v>
+        <v>0.3734</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3157</v>
+        <v>0.759</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5972</v>
+        <v>-0.3856</v>
       </c>
       <c r="V4" t="n">
         <v>0.3018</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3018</v>
+        <v>0.6036</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1623</v>
+        <v>-1.1246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2608</v>
+        <v>-0.0633</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.423</v>
+        <v>-1.0612</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5884</v>
+        <v>-0.3909</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5409</v>
+        <v>-0.5705</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9525</v>
+        <v>0.1796</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8496</v>
+        <v>0.113</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1417</v>
+        <v>0.0634</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9913</v>
+        <v>0.0496</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.438</v>
+        <v>-0.504</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3993</v>
+        <v>-0.6339</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0388</v>
+        <v>0.1299</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.774</v>
+        <v>0.5661</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0334</v>
+        <v>-0.0735</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9399</v>
+        <v>-0.1764</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0936</v>
+        <v>0.1029</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.5508</v>
+        <v>-1.2262</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.8526</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2098</v>
+        <v>-2.1765</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1221</v>
+        <v>-0.3037</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0877</v>
+        <v>-1.8728</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3909</v>
+        <v>-0.5884</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5705</v>
+        <v>-1.5409</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1796</v>
+        <v>0.9525</v>
       </c>
       <c r="J6" t="n">
-        <v>0.113</v>
+        <v>1.8496</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0634</v>
+        <v>-0.1417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0496</v>
+        <v>1.9913</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.504</v>
+        <v>-2.438</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6339</v>
+        <v>-1.3993</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1299</v>
+        <v>-1.0388</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5661</v>
+        <v>3.774</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1587</v>
+        <v>0.0192</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2352</v>
+        <v>0.3754</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0764</v>
+        <v>-0.3562</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2262</v>
+        <v>-2.5508</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2262</v>
+        <v>-2.8526</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2402</v>
+        <v>-2.5182</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8691</v>
+        <v>-4.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6289</v>
+        <v>1.6818</v>
       </c>
       <c r="G7" t="n">
         <v>-3.1273</v>
@@ -1000,13 +1000,13 @@
         <v>3.774</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0041</v>
+        <v>-0.274</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6924</v>
+        <v>0.3614</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6883</v>
+        <v>-0.6354</v>
       </c>
       <c r="V7" t="n">
         <v>0.883</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0045</v>
+        <v>-2.5687</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4598</v>
+        <v>-1.3777</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5448</v>
+        <v>-1.191</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5419</v>
+        <v>0.726</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7109</v>
+        <v>0.3232</v>
       </c>
       <c r="I8" t="n">
-        <v>0.169</v>
+        <v>0.4028</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1323</v>
+        <v>1.2349</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2146</v>
+        <v>-0.1636</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0823</v>
+        <v>1.3984</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4095</v>
+        <v>-0.5089</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4963</v>
+        <v>0.4868</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0868</v>
+        <v>-0.9956</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1887</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.274</v>
+        <v>-0.2382</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5596</v>
+        <v>0.2179</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8335</v>
+        <v>-0.4561</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.4904</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2734</v>
+        <v>-3.1058</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9237</v>
+        <v>-2.6933</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3497</v>
+        <v>-0.4125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.726</v>
+        <v>-2.5419</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3232</v>
+        <v>-2.7109</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4028</v>
+        <v>0.169</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2349</v>
+        <v>-1.1323</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1636</v>
+        <v>-1.2146</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3984</v>
+        <v>0.0823</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5089</v>
+        <v>-1.4095</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4868</v>
+        <v>-1.4963</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9956</v>
+        <v>0.0868</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5661</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9429</v>
+        <v>-0.3752</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3281</v>
+        <v>0.326</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6149</v>
+        <v>-0.7013</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1378</v>
+        <v>-4.3063</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5899</v>
+        <v>-1.7848</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5479</v>
+        <v>-2.5215</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8449</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0629</v>
+        <v>-0.2313</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3092</v>
+        <v>0.1143</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3721</v>
+        <v>-0.3456</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6074</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0522</v>
+        <v>-4.8682</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3785</v>
+        <v>-3.93</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6737</v>
+        <v>-0.9382</v>
       </c>
       <c r="G11" t="n">
         <v>-5.9929</v>
@@ -1312,13 +1312,13 @@
         <v>2.6418</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.659</v>
+        <v>-0.475</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6068</v>
+        <v>-0.1582</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0522</v>
+        <v>-0.3168</v>
       </c>
       <c r="V11" t="n">
         <v>2.7319</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4767</v>
+        <v>-5.4533</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3012</v>
+        <v>-4.4629</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1755</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-7.2511</v>
@@ -1390,13 +1390,13 @@
         <v>3.0192</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1845</v>
+        <v>-1.1611</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1975</v>
+        <v>-0.3593</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.987</v>
+        <v>-0.8018</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0604</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.714</v>
+        <v>-25.1262</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.5855</v>
+        <v>-17.9976</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.128499999999999</v>
+        <v>-7.1286</v>
       </c>
       <c r="G13" t="n">
         <v>-24.6911</v>
@@ -1468,13 +1468,13 @@
         <v>24.531</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.986499999999999</v>
+        <v>-2.3987</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1721</v>
+        <v>1.7598</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1585</v>
+        <v>-4.158700000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.6411</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.9347</v>
+        <v>12.7501</v>
       </c>
       <c r="E14" t="n">
         <v>7.7222</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2125</v>
+        <v>5.0279</v>
       </c>
       <c r="G14" t="n">
         <v>10.2312</v>
@@ -1546,13 +1546,13 @@
         <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3721</v>
+        <v>0.4433</v>
       </c>
       <c r="T14" t="n">
         <v>0.8535</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2256</v>
+        <v>-0.4102</v>
       </c>
       <c r="V14" t="n">
         <v>0.9434</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2347</v>
+        <v>6.8615</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4943</v>
+        <v>0.7866</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7405</v>
+        <v>6.0749</v>
       </c>
       <c r="G15" t="n">
         <v>4.5146</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0117</v>
+        <v>0.6151</v>
       </c>
       <c r="T15" t="n">
-        <v>0.074</v>
+        <v>0.3663</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0857</v>
+        <v>0.2488</v>
       </c>
       <c r="V15" t="n">
         <v>2.864</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7273</v>
+        <v>4.9455</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3872</v>
+        <v>2.6077</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3402</v>
+        <v>2.3378</v>
       </c>
       <c r="G16" t="n">
         <v>2.9677</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>1.703</v>
+        <v>0.9212</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7259</v>
+        <v>0.9464</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0229</v>
+        <v>-0.0252</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8963</v>
+        <v>3.8675</v>
       </c>
       <c r="E17" t="n">
-        <v>2.933</v>
+        <v>2.5433</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9633</v>
+        <v>1.3242</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2651</v>
@@ -1780,13 +1780,13 @@
         <v>2.0757</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0482</v>
+        <v>1.0193</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3144</v>
+        <v>0.9246</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2662</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>1.2262</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.578</v>
+        <v>2.2155</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6215000000000001</v>
+        <v>-0.4267</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1995</v>
+        <v>2.6422</v>
       </c>
       <c r="G18" t="n">
         <v>2.1553</v>
@@ -1858,13 +1858,13 @@
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5397</v>
+        <v>1.1772</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3803</v>
+        <v>0.5752</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1594</v>
+        <v>0.602</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5508999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9772</v>
+        <v>1.5257</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4398</v>
       </c>
       <c r="F19" t="n">
-        <v>1.417</v>
+        <v>1.9655</v>
       </c>
       <c r="G19" t="n">
         <v>3.5146</v>
@@ -1936,13 +1936,13 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0241</v>
+        <v>0.5244</v>
       </c>
       <c r="T19" t="n">
         <v>0.1328</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1569</v>
+        <v>0.3916</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1924</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1008</v>
+        <v>0.6583</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.334</v>
+        <v>1.2927</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2332</v>
+        <v>-0.6344</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9738</v>
+        <v>1.2728</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3572</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3834</v>
+        <v>0.3963</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0223</v>
+        <v>2.1131</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1895</v>
+        <v>0.8295</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1672</v>
+        <v>1.2836</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9515</v>
+        <v>-0.8403</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1677</v>
+        <v>0.047</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2162</v>
+        <v>-0.8873</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.0192</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.9062</v>
+        <v>-2.8305</v>
       </c>
       <c r="R20" t="n">
-        <v>1.887</v>
+        <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2692</v>
+        <v>0.2197</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3803</v>
+        <v>-0.1595</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8889</v>
+        <v>0.3792</v>
       </c>
       <c r="V20" t="n">
         <v>0.6754</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2715</v>
+        <v>-0.2113</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8055</v>
+        <v>-2.334</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0771</v>
+        <v>2.1227</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2728</v>
+        <v>0.9738</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8764999999999999</v>
+        <v>2.3572</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3963</v>
+        <v>-1.3834</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1131</v>
+        <v>0.0223</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8295</v>
+        <v>1.1895</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2836</v>
+        <v>-1.1672</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8403</v>
+        <v>0.9515</v>
       </c>
       <c r="N21" t="n">
-        <v>0.047</v>
+        <v>1.1677</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8873</v>
+        <v>-0.2162</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5096</v>
+        <v>-3.0192</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8305</v>
+        <v>-4.9062</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7101</v>
+        <v>1.1587</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.3803</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0634</v>
+        <v>0.7784</v>
       </c>
       <c r="V21" t="n">
         <v>0.6754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2618</v>
+        <v>-3.6507</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8183</v>
+        <v>-4.6234</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5565</v>
+        <v>0.9727</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6739000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4556</v>
+        <v>0.1555</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0559</v>
+        <v>0.139</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3997</v>
+        <v>0.0165</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3018</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>25.7141</v>
+        <v>28.9621</v>
       </c>
       <c r="E23" t="n">
         <v>7.1286</v>
       </c>
       <c r="F23" t="n">
-        <v>18.5856</v>
+        <v>21.8335</v>
       </c>
       <c r="G23" t="n">
         <v>24.691</v>
@@ -2248,13 +2248,13 @@
         <v>17.9265</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9865</v>
+        <v>6.2344</v>
       </c>
       <c r="T23" t="n">
         <v>4.1586</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1721</v>
+        <v>2.075800000000001</v>
       </c>
       <c r="V23" t="n">
         <v>4.6411</v>
